--- a/files/九龙-西南九龙-汇玺III.xlsx
+++ b/files/九龙-西南九龙-汇玺III.xlsx
@@ -7058,7 +7058,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -26010,7 +26010,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -50072,7 +50072,7 @@
       </c>
       <c r="G1076" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H1076" s="5" t="n">
@@ -56020,7 +56020,7 @@
           <t>F | 271呎 (开放式)
 $684万
 $25,224/呎
-(26年-05月)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
@@ -64458,7 +64458,7 @@
           <t>C | 417呎 (2房)
 $1,161万
 $27,831/呎
-(25年-06月)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E35" s="17" t="inlineStr">

--- a/files/九龙-西南九龙-汇玺III.xlsx
+++ b/files/九龙-西南九龙-汇玺III.xlsx
@@ -665,7 +665,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-西南九龙-汇玺III.xlsx
+++ b/files/九龙-西南九龙-汇玺III.xlsx
@@ -1043,18 +1043,18 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>10079250</v>
+        <v>10751200</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>26455</v>
+        <v>28218</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1105,18 +1105,18 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>11267250</v>
+        <v>12018400</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>28670</v>
+        <v>30581</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1167,18 +1167,18 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>8188500</v>
+        <v>8734400</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>29349</v>
+        <v>31306</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1733,18 +1733,18 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>8138250</v>
+        <v>8680800</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>29169</v>
+        <v>31114</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2291,18 +2291,18 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>8093250</v>
+        <v>8632800</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>29008</v>
+        <v>30942</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -3345,18 +3345,18 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>11026500</v>
+        <v>11761600</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>28057</v>
+        <v>29928</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -3407,18 +3407,18 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>8013000</v>
+        <v>8547200</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>28720</v>
+        <v>30635</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -3965,18 +3965,18 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>7977750</v>
+        <v>8509600</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>28594</v>
+        <v>30500</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -4523,18 +4523,18 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K63" s="5" t="n">
-        <v>7946250</v>
+        <v>8476000</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>28481</v>
+        <v>30380</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -5081,18 +5081,18 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K72" s="5" t="n">
-        <v>7946250</v>
+        <v>8476000</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>28481</v>
+        <v>30380</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -5515,18 +5515,18 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>9608250</v>
+        <v>10248800</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>25219</v>
+        <v>26900</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -5639,18 +5639,18 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>7896000</v>
+        <v>8422400</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>28301</v>
+        <v>30188</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
@@ -6197,18 +6197,18 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K90" s="5" t="n">
-        <v>7871250</v>
+        <v>8396000</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>28212</v>
+        <v>30093</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -6755,18 +6755,18 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K99" s="5" t="n">
-        <v>7845750</v>
+        <v>8368800</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>28121</v>
+        <v>29996</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
@@ -7313,18 +7313,18 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K108" s="5" t="n">
-        <v>7821000</v>
+        <v>8342400</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>28032</v>
+        <v>29901</v>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N108" s="3" t="inlineStr">
@@ -7871,18 +7871,18 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K117" s="5" t="n">
-        <v>7795500</v>
+        <v>8315200</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>27941</v>
+        <v>29804</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -8429,18 +8429,18 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K126" s="5" t="n">
-        <v>7770750</v>
+        <v>8288800</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>27852</v>
+        <v>29709</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -8987,18 +8987,18 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K135" s="5" t="n">
-        <v>7746750</v>
+        <v>8263200</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>27766</v>
+        <v>29617</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N135" s="3" t="inlineStr">
@@ -9545,18 +9545,18 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K144" s="5" t="n">
-        <v>7721250</v>
+        <v>8236000</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>27675</v>
+        <v>29520</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N144" s="3" t="inlineStr">
@@ -11219,18 +11219,18 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K171" s="5" t="n">
-        <v>7656750</v>
+        <v>8167200</v>
       </c>
       <c r="L171" s="5" t="n">
-        <v>27444</v>
+        <v>29273</v>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
@@ -11777,18 +11777,18 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K180" s="5" t="n">
-        <v>7635000</v>
+        <v>8144000</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>27366</v>
+        <v>29190</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N180" s="3" t="inlineStr">
@@ -12211,18 +12211,18 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>9192000</v>
+        <v>9804800</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>24126</v>
+        <v>25734</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N187" s="3" t="inlineStr">
@@ -12335,18 +12335,18 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K189" s="5" t="n">
-        <v>7614750</v>
+        <v>8122400</v>
       </c>
       <c r="L189" s="5" t="n">
-        <v>27293</v>
+        <v>29113</v>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N189" s="3" t="inlineStr">
@@ -12893,18 +12893,18 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>7582500</v>
+        <v>8088000</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>27177</v>
+        <v>28989</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N198" s="3" t="inlineStr">
@@ -14009,18 +14009,18 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K216" s="5" t="n">
-        <v>7518750</v>
+        <v>8020000</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>26949</v>
+        <v>28746</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
@@ -14567,18 +14567,18 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K225" s="5" t="n">
-        <v>7518750</v>
+        <v>8020000</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>26949</v>
+        <v>28746</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -44575,18 +44575,18 @@
       </c>
       <c r="J709" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K709" s="5" t="n">
-        <v>7263000</v>
+        <v>7747200</v>
       </c>
       <c r="L709" s="5" t="n">
-        <v>20517</v>
+        <v>21885</v>
       </c>
       <c r="M709" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N709" s="3" t="inlineStr">
@@ -51333,18 +51333,18 @@
       </c>
       <c r="J818" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K818" s="5" t="n">
-        <v>7431000</v>
+        <v>7926400</v>
       </c>
       <c r="L818" s="5" t="n">
-        <v>19555</v>
+        <v>20859</v>
       </c>
       <c r="M818" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N818" s="3" t="inlineStr">
@@ -72111,18 +72111,18 @@
       </c>
       <c r="J1153" s="3" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="K1153" s="5" t="n">
-        <v>8793750</v>
+        <v>9380000</v>
       </c>
       <c r="L1153" s="5" t="n">
-        <v>25125</v>
+        <v>26800</v>
       </c>
       <c r="M1153" s="3" t="inlineStr">
         <is>
-          <t>90日付款計劃</t>
+          <t>90 日付款計劃</t>
         </is>
       </c>
       <c r="N1153" s="3" t="inlineStr">
